--- a/docs/data/Eichengreen&Saka_BilateralTrust_Database.xlsx
+++ b/docs/data/Eichengreen&Saka_BilateralTrust_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/orkun.saka.3/Dropbox/-- SAKAO/# Research/#7 sovereign_trust/Submissions/JEEA/Final submission/Public data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/orkun.saka.3/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305BD6F1-FFED-F044-A7A5-FE7310F23A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033F7912-5125-3940-AC13-1194516439C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="26" r:id="rId1"/>
@@ -184,27 +184,6 @@
   </si>
   <si>
     <t>Contact</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>When using this database, please cite:</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Eichengreen, B. &amp; Saka, O. (2025). Cultural Stereotypes of Multinational Banks. Journal of the European Economic Association, forthcoming.</t>
-    </r>
   </si>
   <si>
     <t>While we did our best to provide the most accurate information possible, we do not take responsibility for any potential inconsistencies or inaccuracies.</t>
@@ -490,6 +469,46 @@
   </si>
   <si>
     <t>This research was supported by the Clausen Center at the University of California, Berkeley, and a BA/Leverhulme Small Research Grant (SRG21\211248).</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>When using this database, please cite:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Eichengreen, B. &amp; Saka, O. (2026). Cultural Stereotypes of Multinational Banks. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Journal of the European Economic Association</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, Vol. 24, Issue 2, p. 567–609.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1042,7 +1061,7 @@
     </row>
     <row r="2" spans="2:18" s="1" customFormat="1" ht="23" x14ac:dyDescent="0.25">
       <c r="B2" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -1082,7 +1101,7 @@
     </row>
     <row r="4" spans="2:18" s="1" customFormat="1" ht="23" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="15" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
@@ -1144,7 +1163,7 @@
     </row>
     <row r="8" spans="2:18" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="B8" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -1205,7 +1224,7 @@
     </row>
     <row r="11" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B11" s="12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -1266,7 +1285,7 @@
     </row>
     <row r="14" spans="2:18" s="1" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="B14" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -1287,7 +1306,7 @@
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B15" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15" s="12"/>
       <c r="D15" s="12"/>
@@ -1308,7 +1327,7 @@
     </row>
     <row r="16" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
@@ -1348,7 +1367,7 @@
     </row>
     <row r="18" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -1369,10 +1388,10 @@
     </row>
     <row r="19" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -1392,10 +1411,10 @@
     </row>
     <row r="20" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
@@ -1415,10 +1434,10 @@
     </row>
     <row r="21" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -1438,10 +1457,10 @@
     </row>
     <row r="22" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -1461,10 +1480,10 @@
     </row>
     <row r="23" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -1484,10 +1503,10 @@
     </row>
     <row r="24" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -1507,10 +1526,10 @@
     </row>
     <row r="25" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -1530,10 +1549,10 @@
     </row>
     <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -1572,7 +1591,7 @@
     </row>
     <row r="28" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
@@ -1593,7 +1612,7 @@
     </row>
     <row r="29" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
@@ -1614,7 +1633,7 @@
     </row>
     <row r="30" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -1635,7 +1654,7 @@
     </row>
     <row r="31" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
@@ -1694,7 +1713,7 @@
     </row>
     <row r="34" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -1715,7 +1734,7 @@
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B35" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
@@ -1757,7 +1776,7 @@
     </row>
     <row r="37" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
@@ -1807,28 +1826,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>64</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1888,13 +1907,13 @@
         <v>27</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" s="11">
         <v>0.12598429999999999</v>
@@ -1920,7 +1939,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E5" s="11">
         <v>0.18897639999999999</v>
@@ -1940,7 +1959,7 @@
         <v>27</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>2</v>
@@ -1992,7 +2011,7 @@
         <v>27</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>2</v>
@@ -2226,13 +2245,13 @@
         <v>27</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" s="11">
         <v>0.2007874</v>
@@ -2258,7 +2277,7 @@
         <v>2</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E18" s="11">
         <v>0.42913390000000001</v>
@@ -2278,13 +2297,13 @@
         <v>27</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E19" s="11">
         <v>0.18897639999999999</v>
@@ -2330,13 +2349,13 @@
         <v>27</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E21" s="11">
         <v>0.22834650000000001</v>
@@ -2466,7 +2485,7 @@
         <v>2</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E26" s="11">
         <v>0.1023622</v>
@@ -2486,7 +2505,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>2</v>
@@ -2668,13 +2687,13 @@
         <v>28</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C34" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E34" s="11">
         <v>0.1062992</v>
@@ -2700,7 +2719,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E35" s="11">
         <v>0.11023620000000001</v>
@@ -2720,7 +2739,7 @@
         <v>28</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C36" s="8" t="s">
         <v>0</v>
@@ -2772,7 +2791,7 @@
         <v>28</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C38" s="8" t="s">
         <v>0</v>
@@ -3006,13 +3025,13 @@
         <v>28</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C47" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E47" s="11">
         <v>0.13385830000000001</v>
@@ -3038,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E48" s="11">
         <v>0.25984249999999998</v>
@@ -3058,13 +3077,13 @@
         <v>28</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E49" s="11">
         <v>0.12204719999999999</v>
@@ -3110,13 +3129,13 @@
         <v>28</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C51" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E51" s="11">
         <v>0.1496063</v>
@@ -3246,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E56" s="11">
         <v>9.0551199999999998E-2</v>
@@ -3266,7 +3285,7 @@
         <v>28</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>0</v>
@@ -3393,13 +3412,13 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>2</v>
@@ -3419,13 +3438,13 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>0</v>
@@ -3445,16 +3464,16 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E64" s="11">
         <v>0.1490196</v>
@@ -3471,16 +3490,16 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D65" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="D65" s="8" t="s">
-        <v>70</v>
       </c>
       <c r="E65" s="11">
         <v>5.8823500000000001E-2</v>
@@ -3497,13 +3516,13 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B66" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B66" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="C66" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>20</v>
@@ -3523,13 +3542,13 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>7</v>
@@ -3549,13 +3568,13 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>22</v>
@@ -3575,13 +3594,13 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>6</v>
@@ -3601,13 +3620,13 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>5</v>
@@ -3627,13 +3646,13 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>16</v>
@@ -3653,13 +3672,13 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>3</v>
@@ -3679,13 +3698,13 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>17</v>
@@ -3705,13 +3724,13 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>18</v>
@@ -3731,13 +3750,13 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>21</v>
@@ -3757,13 +3776,13 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>14</v>
@@ -3783,16 +3802,16 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E77" s="11">
         <v>9.8039200000000007E-2</v>
@@ -3809,16 +3828,16 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B78" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E78" s="11">
         <v>0.1568628</v>
@@ -3835,16 +3854,16 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E79" s="11">
         <v>9.0196100000000001E-2</v>
@@ -3861,13 +3880,13 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B80" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>12</v>
@@ -3887,16 +3906,16 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E81" s="11">
         <v>8.6274500000000004E-2</v>
@@ -3913,13 +3932,13 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>1</v>
@@ -3939,13 +3958,13 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>13</v>
@@ -3965,13 +3984,13 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>9</v>
@@ -3991,13 +4010,13 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>8</v>
@@ -4017,16 +4036,16 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E86" s="11">
         <v>8.6274500000000004E-2</v>
@@ -4043,13 +4062,13 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>19</v>
@@ -4069,13 +4088,13 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>15</v>
@@ -4095,13 +4114,13 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>10</v>
@@ -4121,13 +4140,13 @@
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>11</v>
@@ -4147,13 +4166,13 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>4</v>
@@ -4179,7 +4198,7 @@
         <v>27</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>2</v>
@@ -4205,7 +4224,7 @@
         <v>28</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>0</v>
@@ -4228,13 +4247,13 @@
         <v>43</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E94" s="11">
         <v>9.9009899999999998E-2</v>
@@ -4257,10 +4276,10 @@
         <v>43</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E95" s="11">
         <v>0.34653460000000003</v>
@@ -4280,10 +4299,10 @@
         <v>43</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>20</v>
@@ -4309,7 +4328,7 @@
         <v>29</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>7</v>
@@ -4332,10 +4351,10 @@
         <v>43</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>22</v>
@@ -4361,7 +4380,7 @@
         <v>30</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>6</v>
@@ -4387,7 +4406,7 @@
         <v>25</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>5</v>
@@ -4413,7 +4432,7 @@
         <v>31</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>16</v>
@@ -4439,7 +4458,7 @@
         <v>23</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>3</v>
@@ -4465,7 +4484,7 @@
         <v>32</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>17</v>
@@ -4491,7 +4510,7 @@
         <v>33</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>18</v>
@@ -4517,7 +4536,7 @@
         <v>34</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>21</v>
@@ -4543,7 +4562,7 @@
         <v>24</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>14</v>
@@ -4566,13 +4585,13 @@
         <v>43</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E107" s="11">
         <v>0.14851490000000001</v>
@@ -4595,10 +4614,10 @@
         <v>44</v>
       </c>
       <c r="C108" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D108" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="D108" s="8" t="s">
-        <v>71</v>
       </c>
       <c r="E108" s="11">
         <v>0.13861390000000001</v>
@@ -4618,13 +4637,13 @@
         <v>43</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E109" s="11">
         <v>0.16831679999999999</v>
@@ -4647,7 +4666,7 @@
         <v>35</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>12</v>
@@ -4670,13 +4689,13 @@
         <v>43</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C111" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E111" s="11">
         <v>0.20792079999999999</v>
@@ -4699,7 +4718,7 @@
         <v>36</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>1</v>
@@ -4725,7 +4744,7 @@
         <v>37</v>
       </c>
       <c r="C113" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D113" s="8" t="s">
         <v>13</v>
@@ -4751,7 +4770,7 @@
         <v>38</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>9</v>
@@ -4777,7 +4796,7 @@
         <v>26</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D115" s="8" t="s">
         <v>8</v>
@@ -4803,10 +4822,10 @@
         <v>45</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E116" s="11">
         <v>0.12871289999999999</v>
@@ -4826,10 +4845,10 @@
         <v>43</v>
       </c>
       <c r="B117" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D117" s="8" t="s">
         <v>19</v>
@@ -4855,7 +4874,7 @@
         <v>39</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D118" s="8" t="s">
         <v>15</v>
@@ -4881,7 +4900,7 @@
         <v>40</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D119" s="8" t="s">
         <v>10</v>
@@ -4907,7 +4926,7 @@
         <v>41</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D120" s="8" t="s">
         <v>11</v>
@@ -4933,7 +4952,7 @@
         <v>42</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D121" s="8" t="s">
         <v>4</v>
@@ -4953,7 +4972,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B122" s="8" t="s">
         <v>27</v>
@@ -4979,7 +4998,7 @@
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B123" s="8" t="s">
         <v>28</v>
@@ -5005,16 +5024,16 @@
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B124" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C124" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E124" s="11">
         <v>4.3137300000000003E-2</v>
@@ -5031,7 +5050,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B125" s="8" t="s">
         <v>43</v>
@@ -5040,7 +5059,7 @@
         <v>20</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E125" s="11">
         <v>5.8823500000000001E-2</v>
@@ -5057,10 +5076,10 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B126" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C126" s="8" t="s">
         <v>20</v>
@@ -5083,7 +5102,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B127" s="8" t="s">
         <v>29</v>
@@ -5109,10 +5128,10 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B128" s="8" t="s">
         <v>54</v>
-      </c>
-      <c r="B128" s="8" t="s">
-        <v>55</v>
       </c>
       <c r="C128" s="8" t="s">
         <v>20</v>
@@ -5135,7 +5154,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B129" s="8" t="s">
         <v>30</v>
@@ -5161,7 +5180,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B130" s="8" t="s">
         <v>25</v>
@@ -5187,7 +5206,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B131" s="8" t="s">
         <v>31</v>
@@ -5213,7 +5232,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B132" s="8" t="s">
         <v>23</v>
@@ -5239,7 +5258,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B133" s="8" t="s">
         <v>32</v>
@@ -5265,7 +5284,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B134" s="8" t="s">
         <v>33</v>
@@ -5291,7 +5310,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B135" s="8" t="s">
         <v>34</v>
@@ -5317,7 +5336,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B136" s="8" t="s">
         <v>24</v>
@@ -5343,16 +5362,16 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B137" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C137" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D137" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E137" s="11">
         <v>8.6274500000000004E-2</v>
@@ -5369,7 +5388,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B138" s="8" t="s">
         <v>44</v>
@@ -5378,7 +5397,7 @@
         <v>20</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E138" s="11">
         <v>0.1254902</v>
@@ -5395,16 +5414,16 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D139" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E139" s="11">
         <v>9.4117599999999996E-2</v>
@@ -5421,7 +5440,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B140" s="8" t="s">
         <v>35</v>
@@ -5447,16 +5466,16 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C141" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E141" s="11">
         <v>9.0196100000000001E-2</v>
@@ -5473,7 +5492,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B142" s="8" t="s">
         <v>36</v>
@@ -5499,7 +5518,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B143" s="8" t="s">
         <v>37</v>
@@ -5525,7 +5544,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B144" s="8" t="s">
         <v>38</v>
@@ -5551,7 +5570,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B145" s="8" t="s">
         <v>26</v>
@@ -5577,7 +5596,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B146" s="8" t="s">
         <v>45</v>
@@ -5586,7 +5605,7 @@
         <v>20</v>
       </c>
       <c r="D146" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E146" s="11">
         <v>3.13726E-2</v>
@@ -5603,10 +5622,10 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B147" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C147" s="8" t="s">
         <v>20</v>
@@ -5629,7 +5648,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B148" s="8" t="s">
         <v>39</v>
@@ -5655,7 +5674,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B149" s="8" t="s">
         <v>40</v>
@@ -5681,7 +5700,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B150" s="8" t="s">
         <v>41</v>
@@ -5707,7 +5726,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B151" s="8" t="s">
         <v>42</v>
@@ -5788,13 +5807,13 @@
         <v>29</v>
       </c>
       <c r="B154" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C154" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D154" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E154" s="11">
         <v>0.1225296</v>
@@ -5820,7 +5839,7 @@
         <v>7</v>
       </c>
       <c r="D155" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E155" s="11">
         <v>0.15019759999999999</v>
@@ -5840,7 +5859,7 @@
         <v>29</v>
       </c>
       <c r="B156" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C156" s="8" t="s">
         <v>7</v>
@@ -5892,7 +5911,7 @@
         <v>29</v>
       </c>
       <c r="B158" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C158" s="8" t="s">
         <v>7</v>
@@ -6126,13 +6145,13 @@
         <v>29</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D167" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E167" s="11">
         <v>0.15810279999999999</v>
@@ -6158,7 +6177,7 @@
         <v>7</v>
       </c>
       <c r="D168" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E168" s="11">
         <v>0.21739130000000001</v>
@@ -6178,13 +6197,13 @@
         <v>29</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C169" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E169" s="11">
         <v>0.13438739999999999</v>
@@ -6230,13 +6249,13 @@
         <v>29</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C171" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D171" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E171" s="11">
         <v>0.15415019999999999</v>
@@ -6366,7 +6385,7 @@
         <v>7</v>
       </c>
       <c r="D176" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E176" s="11">
         <v>9.8814200000000005E-2</v>
@@ -6386,7 +6405,7 @@
         <v>29</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C177" s="8" t="s">
         <v>7</v>
@@ -6513,7 +6532,7 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B182" s="8" t="s">
         <v>27</v>
@@ -6539,7 +6558,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B183" s="8" t="s">
         <v>28</v>
@@ -6565,16 +6584,16 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B184" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C184" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D184" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E184" s="11">
         <v>0.145098</v>
@@ -6591,7 +6610,7 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B185" s="8" t="s">
         <v>43</v>
@@ -6600,7 +6619,7 @@
         <v>22</v>
       </c>
       <c r="D185" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E185" s="11">
         <v>0.145098</v>
@@ -6617,10 +6636,10 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B186" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C186" s="8" t="s">
         <v>22</v>
@@ -6643,7 +6662,7 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B187" s="8" t="s">
         <v>29</v>
@@ -6669,10 +6688,10 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B188" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C188" s="8" t="s">
         <v>22</v>
@@ -6695,7 +6714,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B189" s="8" t="s">
         <v>30</v>
@@ -6721,7 +6740,7 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B190" s="8" t="s">
         <v>25</v>
@@ -6747,7 +6766,7 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B191" s="8" t="s">
         <v>31</v>
@@ -6773,7 +6792,7 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B192" s="8" t="s">
         <v>23</v>
@@ -6799,7 +6818,7 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B193" s="8" t="s">
         <v>32</v>
@@ -6825,7 +6844,7 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B194" s="8" t="s">
         <v>33</v>
@@ -6851,7 +6870,7 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B195" s="8" t="s">
         <v>34</v>
@@ -6877,7 +6896,7 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B196" s="8" t="s">
         <v>24</v>
@@ -6903,16 +6922,16 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B197" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C197" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D197" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E197" s="11">
         <v>0.31372549999999999</v>
@@ -6929,7 +6948,7 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B198" s="8" t="s">
         <v>44</v>
@@ -6938,7 +6957,7 @@
         <v>22</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E198" s="11">
         <v>0.27450980000000003</v>
@@ -6955,16 +6974,16 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B199" s="8" t="s">
         <v>55</v>
-      </c>
-      <c r="B199" s="8" t="s">
-        <v>56</v>
       </c>
       <c r="C199" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D199" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E199" s="11">
         <v>0.27450980000000003</v>
@@ -6981,7 +7000,7 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B200" s="8" t="s">
         <v>35</v>
@@ -7007,16 +7026,16 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B201" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C201" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D201" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E201" s="11">
         <v>0.23137260000000001</v>
@@ -7033,7 +7052,7 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B202" s="8" t="s">
         <v>36</v>
@@ -7059,7 +7078,7 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B203" s="8" t="s">
         <v>37</v>
@@ -7085,7 +7104,7 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B204" s="8" t="s">
         <v>38</v>
@@ -7111,7 +7130,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B205" s="8" t="s">
         <v>26</v>
@@ -7137,7 +7156,7 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>45</v>
@@ -7146,7 +7165,7 @@
         <v>22</v>
       </c>
       <c r="D206" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E206" s="11">
         <v>0.145098</v>
@@ -7163,10 +7182,10 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B207" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C207" s="8" t="s">
         <v>22</v>
@@ -7189,7 +7208,7 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B208" s="8" t="s">
         <v>39</v>
@@ -7215,7 +7234,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B209" s="8" t="s">
         <v>40</v>
@@ -7241,7 +7260,7 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B210" s="8" t="s">
         <v>41</v>
@@ -7267,7 +7286,7 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B211" s="8" t="s">
         <v>42</v>
@@ -7348,13 +7367,13 @@
         <v>30</v>
       </c>
       <c r="B214" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C214" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D214" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E214" s="11">
         <v>0.12941179999999999</v>
@@ -7380,7 +7399,7 @@
         <v>6</v>
       </c>
       <c r="D215" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E215" s="11">
         <v>0.13725490000000001</v>
@@ -7400,7 +7419,7 @@
         <v>30</v>
       </c>
       <c r="B216" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C216" s="8" t="s">
         <v>6</v>
@@ -7452,7 +7471,7 @@
         <v>30</v>
       </c>
       <c r="B218" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C218" s="8" t="s">
         <v>6</v>
@@ -7686,13 +7705,13 @@
         <v>30</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C227" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E227" s="11">
         <v>0.1490196</v>
@@ -7718,7 +7737,7 @@
         <v>6</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E228" s="11">
         <v>0.22745099999999999</v>
@@ -7738,13 +7757,13 @@
         <v>30</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C229" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E229" s="11">
         <v>0.14117650000000001</v>
@@ -7790,13 +7809,13 @@
         <v>30</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C231" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D231" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E231" s="11">
         <v>0.145098</v>
@@ -7926,7 +7945,7 @@
         <v>6</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E236" s="11">
         <v>8.6274500000000004E-2</v>
@@ -7946,7 +7965,7 @@
         <v>30</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C237" s="8" t="s">
         <v>6</v>
@@ -8128,13 +8147,13 @@
         <v>25</v>
       </c>
       <c r="B244" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C244" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D244" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E244" s="11">
         <v>6.6666699999999995E-2</v>
@@ -8160,7 +8179,7 @@
         <v>5</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E245" s="11">
         <v>6.6666699999999995E-2</v>
@@ -8180,7 +8199,7 @@
         <v>25</v>
       </c>
       <c r="B246" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C246" s="8" t="s">
         <v>5</v>
@@ -8232,7 +8251,7 @@
         <v>25</v>
       </c>
       <c r="B248" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C248" s="8" t="s">
         <v>5</v>
@@ -8466,13 +8485,13 @@
         <v>25</v>
       </c>
       <c r="B257" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C257" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E257" s="11">
         <v>0.1019608</v>
@@ -8498,7 +8517,7 @@
         <v>5</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E258" s="11">
         <v>0.145098</v>
@@ -8518,13 +8537,13 @@
         <v>25</v>
       </c>
       <c r="B259" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C259" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E259" s="11">
         <v>8.6274500000000004E-2</v>
@@ -8570,13 +8589,13 @@
         <v>25</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C261" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E261" s="11">
         <v>0.1058824</v>
@@ -8706,7 +8725,7 @@
         <v>5</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E266" s="11">
         <v>7.4509800000000001E-2</v>
@@ -8726,7 +8745,7 @@
         <v>25</v>
       </c>
       <c r="B267" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C267" s="8" t="s">
         <v>5</v>
@@ -8908,13 +8927,13 @@
         <v>31</v>
       </c>
       <c r="B274" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C274" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D274" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E274" s="11">
         <v>0.13385830000000001</v>
@@ -8940,7 +8959,7 @@
         <v>16</v>
       </c>
       <c r="D275" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E275" s="11">
         <v>0.15354329999999999</v>
@@ -8960,7 +8979,7 @@
         <v>31</v>
       </c>
       <c r="B276" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C276" s="8" t="s">
         <v>16</v>
@@ -9012,7 +9031,7 @@
         <v>31</v>
       </c>
       <c r="B278" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C278" s="8" t="s">
         <v>16</v>
@@ -9246,13 +9265,13 @@
         <v>31</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C287" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E287" s="11">
         <v>0.24409449999999999</v>
@@ -9278,7 +9297,7 @@
         <v>16</v>
       </c>
       <c r="D288" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E288" s="11">
         <v>0.40157480000000001</v>
@@ -9298,13 +9317,13 @@
         <v>31</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C289" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D289" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E289" s="11">
         <v>0.19685040000000001</v>
@@ -9350,13 +9369,13 @@
         <v>31</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C291" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D291" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E291" s="11">
         <v>0.19685040000000001</v>
@@ -9486,7 +9505,7 @@
         <v>16</v>
       </c>
       <c r="D296" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E296" s="11">
         <v>0.1062992</v>
@@ -9506,7 +9525,7 @@
         <v>31</v>
       </c>
       <c r="B297" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C297" s="8" t="s">
         <v>16</v>
@@ -9688,13 +9707,13 @@
         <v>23</v>
       </c>
       <c r="B304" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C304" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D304" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E304" s="11">
         <v>9.5617499999999994E-2</v>
@@ -9720,7 +9739,7 @@
         <v>3</v>
       </c>
       <c r="D305" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E305" s="11">
         <v>0.36653390000000002</v>
@@ -9740,7 +9759,7 @@
         <v>23</v>
       </c>
       <c r="B306" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C306" s="8" t="s">
         <v>3</v>
@@ -9792,7 +9811,7 @@
         <v>23</v>
       </c>
       <c r="B308" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C308" s="8" t="s">
         <v>3</v>
@@ -10026,13 +10045,13 @@
         <v>23</v>
       </c>
       <c r="B317" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C317" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E317" s="11">
         <v>0.12748999999999999</v>
@@ -10058,7 +10077,7 @@
         <v>3</v>
       </c>
       <c r="D318" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E318" s="11">
         <v>0.14342630000000001</v>
@@ -10078,13 +10097,13 @@
         <v>23</v>
       </c>
       <c r="B319" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C319" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E319" s="11">
         <v>0.123506</v>
@@ -10130,13 +10149,13 @@
         <v>23</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C321" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E321" s="11">
         <v>0.14342630000000001</v>
@@ -10266,7 +10285,7 @@
         <v>3</v>
       </c>
       <c r="D326" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E326" s="11">
         <v>0.13944219999999999</v>
@@ -10286,7 +10305,7 @@
         <v>23</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C327" s="8" t="s">
         <v>3</v>
@@ -10468,13 +10487,13 @@
         <v>32</v>
       </c>
       <c r="B334" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C334" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D334" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E334" s="11">
         <v>9.0551199999999998E-2</v>
@@ -10500,7 +10519,7 @@
         <v>17</v>
       </c>
       <c r="D335" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E335" s="11">
         <v>0.18503939999999999</v>
@@ -10520,7 +10539,7 @@
         <v>32</v>
       </c>
       <c r="B336" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C336" s="8" t="s">
         <v>17</v>
@@ -10572,7 +10591,7 @@
         <v>32</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C338" s="8" t="s">
         <v>17</v>
@@ -10806,13 +10825,13 @@
         <v>32</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C347" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D347" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E347" s="11">
         <v>0.19685040000000001</v>
@@ -10838,7 +10857,7 @@
         <v>17</v>
       </c>
       <c r="D348" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E348" s="11">
         <v>0.27559050000000002</v>
@@ -10858,13 +10877,13 @@
         <v>32</v>
       </c>
       <c r="B349" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C349" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D349" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E349" s="11">
         <v>0.16535430000000001</v>
@@ -10910,13 +10929,13 @@
         <v>32</v>
       </c>
       <c r="B351" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C351" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D351" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E351" s="11">
         <v>0.27165349999999999</v>
@@ -11046,7 +11065,7 @@
         <v>17</v>
       </c>
       <c r="D356" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E356" s="11">
         <v>7.48032E-2</v>
@@ -11066,7 +11085,7 @@
         <v>32</v>
       </c>
       <c r="B357" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C357" s="8" t="s">
         <v>17</v>
@@ -11248,13 +11267,13 @@
         <v>33</v>
       </c>
       <c r="B364" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C364" s="8" t="s">
         <v>18</v>
       </c>
       <c r="D364" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E364" s="11">
         <v>0.38</v>
@@ -11280,7 +11299,7 @@
         <v>18</v>
       </c>
       <c r="D365" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E365" s="11">
         <v>0.39</v>
@@ -11300,7 +11319,7 @@
         <v>33</v>
       </c>
       <c r="B366" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C366" s="8" t="s">
         <v>18</v>
@@ -11352,7 +11371,7 @@
         <v>33</v>
       </c>
       <c r="B368" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C368" s="8" t="s">
         <v>18</v>
@@ -11586,13 +11605,13 @@
         <v>33</v>
       </c>
       <c r="B377" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C377" s="8" t="s">
         <v>18</v>
       </c>
       <c r="D377" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E377" s="11">
         <v>0.41</v>
@@ -11618,7 +11637,7 @@
         <v>18</v>
       </c>
       <c r="D378" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E378" s="11">
         <v>0.42</v>
@@ -11638,13 +11657,13 @@
         <v>33</v>
       </c>
       <c r="B379" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C379" s="8" t="s">
         <v>18</v>
       </c>
       <c r="D379" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E379" s="11">
         <v>0.39</v>
@@ -11690,13 +11709,13 @@
         <v>33</v>
       </c>
       <c r="B381" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C381" s="8" t="s">
         <v>18</v>
       </c>
       <c r="D381" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E381" s="11">
         <v>0.38</v>
@@ -11826,7 +11845,7 @@
         <v>18</v>
       </c>
       <c r="D386" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E386" s="11">
         <v>0.37</v>
@@ -11846,7 +11865,7 @@
         <v>33</v>
       </c>
       <c r="B387" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C387" s="8" t="s">
         <v>18</v>
@@ -12028,13 +12047,13 @@
         <v>34</v>
       </c>
       <c r="B394" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C394" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D394" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E394" s="11">
         <v>0.1023622</v>
@@ -12060,7 +12079,7 @@
         <v>21</v>
       </c>
       <c r="D395" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E395" s="11">
         <v>0.1023622</v>
@@ -12080,7 +12099,7 @@
         <v>34</v>
       </c>
       <c r="B396" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C396" s="8" t="s">
         <v>21</v>
@@ -12132,7 +12151,7 @@
         <v>34</v>
       </c>
       <c r="B398" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C398" s="8" t="s">
         <v>21</v>
@@ -12366,13 +12385,13 @@
         <v>34</v>
       </c>
       <c r="B407" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C407" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D407" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E407" s="11">
         <v>0.12992129999999999</v>
@@ -12398,7 +12417,7 @@
         <v>21</v>
       </c>
       <c r="D408" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E408" s="11">
         <v>0.15354329999999999</v>
@@ -12418,13 +12437,13 @@
         <v>34</v>
       </c>
       <c r="B409" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C409" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D409" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E409" s="11">
         <v>0.12598429999999999</v>
@@ -12470,13 +12489,13 @@
         <v>34</v>
       </c>
       <c r="B411" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C411" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D411" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E411" s="11">
         <v>0.19685040000000001</v>
@@ -12606,7 +12625,7 @@
         <v>21</v>
       </c>
       <c r="D416" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E416" s="11">
         <v>0.1023622</v>
@@ -12626,7 +12645,7 @@
         <v>34</v>
       </c>
       <c r="B417" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C417" s="8" t="s">
         <v>21</v>
@@ -12808,13 +12827,13 @@
         <v>24</v>
       </c>
       <c r="B424" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C424" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D424" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E424" s="11">
         <v>8.2677200000000006E-2</v>
@@ -12840,7 +12859,7 @@
         <v>14</v>
       </c>
       <c r="D425" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E425" s="11">
         <v>9.4488199999999994E-2</v>
@@ -12860,7 +12879,7 @@
         <v>24</v>
       </c>
       <c r="B426" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C426" s="8" t="s">
         <v>14</v>
@@ -12912,7 +12931,7 @@
         <v>24</v>
       </c>
       <c r="B428" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C428" s="8" t="s">
         <v>14</v>
@@ -13146,13 +13165,13 @@
         <v>24</v>
       </c>
       <c r="B437" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C437" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D437" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E437" s="11">
         <v>0.1141732</v>
@@ -13178,7 +13197,7 @@
         <v>14</v>
       </c>
       <c r="D438" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E438" s="11">
         <v>0.1811024</v>
@@ -13198,13 +13217,13 @@
         <v>24</v>
       </c>
       <c r="B439" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C439" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D439" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E439" s="11">
         <v>0.1062992</v>
@@ -13250,13 +13269,13 @@
         <v>24</v>
       </c>
       <c r="B441" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C441" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D441" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E441" s="11">
         <v>0.12992129999999999</v>
@@ -13386,7 +13405,7 @@
         <v>14</v>
       </c>
       <c r="D446" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E446" s="11">
         <v>6.2992099999999995E-2</v>
@@ -13406,7 +13425,7 @@
         <v>24</v>
       </c>
       <c r="B447" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C447" s="8" t="s">
         <v>14</v>
@@ -13533,13 +13552,13 @@
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B452" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C452" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D452" s="8" t="s">
         <v>2</v>
@@ -13559,13 +13578,13 @@
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B453" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C453" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D453" s="8" t="s">
         <v>0</v>
@@ -13585,16 +13604,16 @@
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B454" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C454" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D454" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E454" s="11">
         <v>9.4488199999999994E-2</v>
@@ -13611,16 +13630,16 @@
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B455" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C455" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D455" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E455" s="11">
         <v>0.1181102</v>
@@ -13637,13 +13656,13 @@
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B456" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C456" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D456" s="8" t="s">
         <v>20</v>
@@ -13663,13 +13682,13 @@
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B457" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C457" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D457" s="8" t="s">
         <v>7</v>
@@ -13689,13 +13708,13 @@
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A458" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B458" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C458" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D458" s="8" t="s">
         <v>22</v>
@@ -13715,13 +13734,13 @@
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B459" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C459" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D459" s="8" t="s">
         <v>6</v>
@@ -13741,13 +13760,13 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B460" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C460" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D460" s="8" t="s">
         <v>5</v>
@@ -13767,13 +13786,13 @@
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B461" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C461" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D461" s="8" t="s">
         <v>16</v>
@@ -13793,13 +13812,13 @@
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B462" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C462" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D462" s="8" t="s">
         <v>3</v>
@@ -13819,13 +13838,13 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B463" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C463" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D463" s="8" t="s">
         <v>17</v>
@@ -13845,13 +13864,13 @@
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A464" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B464" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C464" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D464" s="8" t="s">
         <v>18</v>
@@ -13871,13 +13890,13 @@
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A465" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B465" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C465" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D465" s="8" t="s">
         <v>21</v>
@@ -13897,13 +13916,13 @@
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A466" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B466" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C466" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D466" s="8" t="s">
         <v>14</v>
@@ -13923,16 +13942,16 @@
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A467" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B467" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C467" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D467" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E467" s="11">
         <v>0.3543307</v>
@@ -13949,16 +13968,16 @@
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B468" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C468" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D468" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E468" s="11">
         <v>0.2086614</v>
@@ -13975,16 +13994,16 @@
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A469" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B469" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C469" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D469" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E469" s="11">
         <v>0.30708659999999999</v>
@@ -14001,13 +14020,13 @@
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A470" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B470" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C470" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D470" s="8" t="s">
         <v>12</v>
@@ -14027,16 +14046,16 @@
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A471" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="B471" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B471" s="8" t="s">
-        <v>58</v>
-      </c>
       <c r="C471" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D471" s="8" t="s">
         <v>73</v>
-      </c>
-      <c r="D471" s="8" t="s">
-        <v>74</v>
       </c>
       <c r="E471" s="11">
         <v>0.1732284</v>
@@ -14053,13 +14072,13 @@
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A472" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B472" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C472" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D472" s="8" t="s">
         <v>1</v>
@@ -14079,13 +14098,13 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B473" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C473" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D473" s="8" t="s">
         <v>13</v>
@@ -14105,13 +14124,13 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A474" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B474" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C474" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D474" s="8" t="s">
         <v>9</v>
@@ -14131,13 +14150,13 @@
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B475" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C475" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D475" s="8" t="s">
         <v>8</v>
@@ -14157,16 +14176,16 @@
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A476" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B476" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C476" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D476" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E476" s="11">
         <v>0.13385830000000001</v>
@@ -14183,13 +14202,13 @@
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A477" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B477" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C477" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D477" s="8" t="s">
         <v>19</v>
@@ -14209,13 +14228,13 @@
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A478" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B478" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C478" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D478" s="8" t="s">
         <v>15</v>
@@ -14235,13 +14254,13 @@
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A479" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B479" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C479" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D479" s="8" t="s">
         <v>10</v>
@@ -14261,13 +14280,13 @@
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A480" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B480" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C480" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D480" s="8" t="s">
         <v>11</v>
@@ -14287,13 +14306,13 @@
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A481" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B481" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C481" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D481" s="8" t="s">
         <v>4</v>
@@ -14319,7 +14338,7 @@
         <v>27</v>
       </c>
       <c r="C482" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D482" s="8" t="s">
         <v>2</v>
@@ -14345,7 +14364,7 @@
         <v>28</v>
       </c>
       <c r="C483" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D483" s="8" t="s">
         <v>0</v>
@@ -14368,13 +14387,13 @@
         <v>44</v>
       </c>
       <c r="B484" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C484" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D484" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E484" s="11">
         <v>6.9306900000000005E-2</v>
@@ -14397,10 +14416,10 @@
         <v>43</v>
       </c>
       <c r="C485" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D485" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E485" s="11">
         <v>0.12871289999999999</v>
@@ -14420,10 +14439,10 @@
         <v>44</v>
       </c>
       <c r="B486" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C486" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D486" s="8" t="s">
         <v>20</v>
@@ -14449,7 +14468,7 @@
         <v>29</v>
       </c>
       <c r="C487" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D487" s="8" t="s">
         <v>7</v>
@@ -14472,10 +14491,10 @@
         <v>44</v>
       </c>
       <c r="B488" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C488" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D488" s="8" t="s">
         <v>22</v>
@@ -14501,7 +14520,7 @@
         <v>30</v>
       </c>
       <c r="C489" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D489" s="8" t="s">
         <v>6</v>
@@ -14527,7 +14546,7 @@
         <v>25</v>
       </c>
       <c r="C490" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D490" s="8" t="s">
         <v>5</v>
@@ -14553,7 +14572,7 @@
         <v>31</v>
       </c>
       <c r="C491" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D491" s="8" t="s">
         <v>16</v>
@@ -14579,7 +14598,7 @@
         <v>23</v>
       </c>
       <c r="C492" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D492" s="8" t="s">
         <v>3</v>
@@ -14605,7 +14624,7 @@
         <v>32</v>
       </c>
       <c r="C493" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D493" s="8" t="s">
         <v>17</v>
@@ -14631,7 +14650,7 @@
         <v>33</v>
       </c>
       <c r="C494" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D494" s="8" t="s">
         <v>18</v>
@@ -14657,7 +14676,7 @@
         <v>34</v>
       </c>
       <c r="C495" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D495" s="8" t="s">
         <v>21</v>
@@ -14683,7 +14702,7 @@
         <v>24</v>
       </c>
       <c r="C496" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D496" s="8" t="s">
         <v>14</v>
@@ -14706,13 +14725,13 @@
         <v>44</v>
       </c>
       <c r="B497" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C497" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D497" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E497" s="11">
         <v>0.14851490000000001</v>
@@ -14735,10 +14754,10 @@
         <v>44</v>
       </c>
       <c r="C498" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D498" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E498" s="11">
         <v>0.34653460000000003</v>
@@ -14758,13 +14777,13 @@
         <v>44</v>
       </c>
       <c r="B499" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C499" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D499" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D499" s="8" t="s">
-        <v>72</v>
       </c>
       <c r="E499" s="11">
         <v>0.16831679999999999</v>
@@ -14787,7 +14806,7 @@
         <v>35</v>
       </c>
       <c r="C500" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D500" s="8" t="s">
         <v>12</v>
@@ -14810,13 +14829,13 @@
         <v>44</v>
       </c>
       <c r="B501" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C501" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D501" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E501" s="11">
         <v>0.17821780000000001</v>
@@ -14839,7 +14858,7 @@
         <v>36</v>
       </c>
       <c r="C502" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D502" s="8" t="s">
         <v>1</v>
@@ -14865,7 +14884,7 @@
         <v>37</v>
       </c>
       <c r="C503" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D503" s="8" t="s">
         <v>13</v>
@@ -14891,7 +14910,7 @@
         <v>38</v>
       </c>
       <c r="C504" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D504" s="8" t="s">
         <v>9</v>
@@ -14917,7 +14936,7 @@
         <v>26</v>
       </c>
       <c r="C505" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D505" s="8" t="s">
         <v>8</v>
@@ -14943,10 +14962,10 @@
         <v>45</v>
       </c>
       <c r="C506" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D506" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E506" s="11">
         <v>8.9108900000000005E-2</v>
@@ -14966,10 +14985,10 @@
         <v>44</v>
       </c>
       <c r="B507" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C507" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D507" s="8" t="s">
         <v>19</v>
@@ -14995,7 +15014,7 @@
         <v>39</v>
       </c>
       <c r="C508" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D508" s="8" t="s">
         <v>15</v>
@@ -15021,7 +15040,7 @@
         <v>40</v>
       </c>
       <c r="C509" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D509" s="8" t="s">
         <v>10</v>
@@ -15047,7 +15066,7 @@
         <v>41</v>
       </c>
       <c r="C510" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D510" s="8" t="s">
         <v>11</v>
@@ -15073,7 +15092,7 @@
         <v>42</v>
       </c>
       <c r="C511" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D511" s="8" t="s">
         <v>4</v>
@@ -15093,13 +15112,13 @@
     </row>
     <row r="512" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A512" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B512" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C512" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D512" s="8" t="s">
         <v>2</v>
@@ -15119,13 +15138,13 @@
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A513" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B513" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C513" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D513" s="8" t="s">
         <v>0</v>
@@ -15145,16 +15164,16 @@
     </row>
     <row r="514" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A514" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B514" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C514" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D514" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E514" s="11">
         <v>0.12598429999999999</v>
@@ -15171,16 +15190,16 @@
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A515" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B515" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C515" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D515" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E515" s="11">
         <v>0.1771654</v>
@@ -15197,13 +15216,13 @@
     </row>
     <row r="516" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A516" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B516" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C516" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D516" s="8" t="s">
         <v>20</v>
@@ -15223,13 +15242,13 @@
     </row>
     <row r="517" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A517" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B517" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C517" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D517" s="8" t="s">
         <v>7</v>
@@ -15249,13 +15268,13 @@
     </row>
     <row r="518" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A518" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B518" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C518" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D518" s="8" t="s">
         <v>22</v>
@@ -15275,13 +15294,13 @@
     </row>
     <row r="519" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A519" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B519" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C519" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D519" s="8" t="s">
         <v>6</v>
@@ -15301,13 +15320,13 @@
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A520" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B520" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C520" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D520" s="8" t="s">
         <v>5</v>
@@ -15327,13 +15346,13 @@
     </row>
     <row r="521" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A521" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B521" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C521" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D521" s="8" t="s">
         <v>16</v>
@@ -15353,13 +15372,13 @@
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A522" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B522" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C522" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D522" s="8" t="s">
         <v>3</v>
@@ -15379,13 +15398,13 @@
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A523" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B523" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C523" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D523" s="8" t="s">
         <v>17</v>
@@ -15405,13 +15424,13 @@
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A524" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B524" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C524" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D524" s="8" t="s">
         <v>18</v>
@@ -15431,13 +15450,13 @@
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A525" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B525" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C525" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D525" s="8" t="s">
         <v>21</v>
@@ -15457,13 +15476,13 @@
     </row>
     <row r="526" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A526" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B526" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C526" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D526" s="8" t="s">
         <v>14</v>
@@ -15483,16 +15502,16 @@
     </row>
     <row r="527" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A527" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B527" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B527" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="C527" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D527" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="D527" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="E527" s="11">
         <v>0.39763779999999999</v>
@@ -15509,16 +15528,16 @@
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A528" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B528" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C528" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D528" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E528" s="11">
         <v>0.25196849999999998</v>
@@ -15535,16 +15554,16 @@
     </row>
     <row r="529" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A529" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B529" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C529" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D529" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E529" s="11">
         <v>0.44094489999999997</v>
@@ -15561,13 +15580,13 @@
     </row>
     <row r="530" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A530" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B530" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C530" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D530" s="8" t="s">
         <v>12</v>
@@ -15587,16 +15606,16 @@
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A531" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B531" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C531" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D531" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E531" s="11">
         <v>0.21653539999999999</v>
@@ -15613,13 +15632,13 @@
     </row>
     <row r="532" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A532" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B532" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C532" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D532" s="8" t="s">
         <v>1</v>
@@ -15639,13 +15658,13 @@
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A533" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B533" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C533" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D533" s="8" t="s">
         <v>13</v>
@@ -15665,13 +15684,13 @@
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A534" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B534" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C534" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D534" s="8" t="s">
         <v>9</v>
@@ -15691,13 +15710,13 @@
     </row>
     <row r="535" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A535" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B535" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C535" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D535" s="8" t="s">
         <v>8</v>
@@ -15717,16 +15736,16 @@
     </row>
     <row r="536" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A536" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B536" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C536" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D536" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E536" s="11">
         <v>0.1496063</v>
@@ -15743,13 +15762,13 @@
     </row>
     <row r="537" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A537" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B537" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C537" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D537" s="8" t="s">
         <v>19</v>
@@ -15769,13 +15788,13 @@
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A538" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B538" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C538" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D538" s="8" t="s">
         <v>15</v>
@@ -15795,13 +15814,13 @@
     </row>
     <row r="539" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A539" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B539" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C539" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D539" s="8" t="s">
         <v>10</v>
@@ -15821,13 +15840,13 @@
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A540" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B540" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C540" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D540" s="8" t="s">
         <v>11</v>
@@ -15847,13 +15866,13 @@
     </row>
     <row r="541" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A541" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B541" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C541" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D541" s="8" t="s">
         <v>4</v>
@@ -15928,13 +15947,13 @@
         <v>35</v>
       </c>
       <c r="B544" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C544" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D544" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E544" s="11">
         <v>0.17647060000000001</v>
@@ -15960,7 +15979,7 @@
         <v>12</v>
       </c>
       <c r="D545" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E545" s="11">
         <v>0.18627450000000001</v>
@@ -15980,7 +15999,7 @@
         <v>35</v>
       </c>
       <c r="B546" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C546" s="8" t="s">
         <v>12</v>
@@ -16032,7 +16051,7 @@
         <v>35</v>
       </c>
       <c r="B548" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C548" s="8" t="s">
         <v>12</v>
@@ -16266,13 +16285,13 @@
         <v>35</v>
       </c>
       <c r="B557" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C557" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D557" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E557" s="11">
         <v>0.23529410000000001</v>
@@ -16298,7 +16317,7 @@
         <v>12</v>
       </c>
       <c r="D558" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E558" s="11">
         <v>0.30392160000000001</v>
@@ -16318,13 +16337,13 @@
         <v>35</v>
       </c>
       <c r="B559" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C559" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D559" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E559" s="11">
         <v>0.24509800000000001</v>
@@ -16370,13 +16389,13 @@
         <v>35</v>
       </c>
       <c r="B561" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C561" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D561" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E561" s="11">
         <v>0.26470589999999999</v>
@@ -16506,7 +16525,7 @@
         <v>12</v>
       </c>
       <c r="D566" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E566" s="11">
         <v>0.18627450000000001</v>
@@ -16526,7 +16545,7 @@
         <v>35</v>
       </c>
       <c r="B567" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C567" s="8" t="s">
         <v>12</v>
@@ -16653,13 +16672,13 @@
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A572" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B572" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C572" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D572" s="8" t="s">
         <v>2</v>
@@ -16679,13 +16698,13 @@
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A573" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B573" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C573" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D573" s="8" t="s">
         <v>0</v>
@@ -16705,16 +16724,16 @@
     </row>
     <row r="574" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A574" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B574" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C574" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D574" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E574" s="11">
         <v>8.9108900000000005E-2</v>
@@ -16731,16 +16750,16 @@
     </row>
     <row r="575" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A575" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B575" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C575" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D575" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E575" s="11">
         <v>0.1188119</v>
@@ -16757,13 +16776,13 @@
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A576" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B576" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C576" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D576" s="8" t="s">
         <v>20</v>
@@ -16783,13 +16802,13 @@
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A577" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B577" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C577" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D577" s="8" t="s">
         <v>7</v>
@@ -16809,13 +16828,13 @@
     </row>
     <row r="578" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A578" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B578" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C578" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D578" s="8" t="s">
         <v>22</v>
@@ -16835,13 +16854,13 @@
     </row>
     <row r="579" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A579" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B579" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C579" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D579" s="8" t="s">
         <v>6</v>
@@ -16861,13 +16880,13 @@
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A580" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B580" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C580" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D580" s="8" t="s">
         <v>5</v>
@@ -16887,13 +16906,13 @@
     </row>
     <row r="581" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A581" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B581" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C581" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D581" s="8" t="s">
         <v>16</v>
@@ -16913,13 +16932,13 @@
     </row>
     <row r="582" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A582" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B582" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C582" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D582" s="8" t="s">
         <v>3</v>
@@ -16939,13 +16958,13 @@
     </row>
     <row r="583" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A583" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B583" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C583" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D583" s="8" t="s">
         <v>17</v>
@@ -16965,13 +16984,13 @@
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A584" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B584" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C584" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D584" s="8" t="s">
         <v>18</v>
@@ -16991,13 +17010,13 @@
     </row>
     <row r="585" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A585" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B585" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C585" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D585" s="8" t="s">
         <v>21</v>
@@ -17017,13 +17036,13 @@
     </row>
     <row r="586" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A586" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B586" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C586" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D586" s="8" t="s">
         <v>14</v>
@@ -17043,16 +17062,16 @@
     </row>
     <row r="587" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A587" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B587" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C587" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D587" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E587" s="11">
         <v>0.1089109</v>
@@ -17069,16 +17088,16 @@
     </row>
     <row r="588" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A588" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B588" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C588" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D588" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E588" s="11">
         <v>0.13861390000000001</v>
@@ -17095,16 +17114,16 @@
     </row>
     <row r="589" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A589" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B589" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C589" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D589" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E589" s="11">
         <v>0.13861390000000001</v>
@@ -17121,13 +17140,13 @@
     </row>
     <row r="590" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A590" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B590" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C590" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D590" s="8" t="s">
         <v>12</v>
@@ -17147,16 +17166,16 @@
     </row>
     <row r="591" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A591" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B591" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C591" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D591" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E591" s="11">
         <v>0.2376238</v>
@@ -17173,13 +17192,13 @@
     </row>
     <row r="592" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A592" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B592" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C592" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D592" s="8" t="s">
         <v>1</v>
@@ -17199,13 +17218,13 @@
     </row>
     <row r="593" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A593" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B593" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C593" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D593" s="8" t="s">
         <v>13</v>
@@ -17225,13 +17244,13 @@
     </row>
     <row r="594" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A594" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B594" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C594" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D594" s="8" t="s">
         <v>9</v>
@@ -17251,13 +17270,13 @@
     </row>
     <row r="595" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A595" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B595" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C595" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D595" s="8" t="s">
         <v>8</v>
@@ -17277,16 +17296,16 @@
     </row>
     <row r="596" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A596" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B596" s="8" t="s">
         <v>45</v>
       </c>
       <c r="C596" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D596" s="8" t="s">
         <v>74</v>
-      </c>
-      <c r="D596" s="8" t="s">
-        <v>75</v>
       </c>
       <c r="E596" s="11">
         <v>9.9009899999999998E-2</v>
@@ -17303,13 +17322,13 @@
     </row>
     <row r="597" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A597" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B597" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B597" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="C597" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D597" s="8" t="s">
         <v>19</v>
@@ -17329,13 +17348,13 @@
     </row>
     <row r="598" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A598" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B598" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C598" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D598" s="8" t="s">
         <v>15</v>
@@ -17355,13 +17374,13 @@
     </row>
     <row r="599" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A599" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B599" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C599" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D599" s="8" t="s">
         <v>10</v>
@@ -17381,13 +17400,13 @@
     </row>
     <row r="600" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A600" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B600" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C600" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D600" s="8" t="s">
         <v>11</v>
@@ -17407,13 +17426,13 @@
     </row>
     <row r="601" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A601" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B601" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C601" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D601" s="8" t="s">
         <v>4</v>
@@ -17488,13 +17507,13 @@
         <v>36</v>
       </c>
       <c r="B604" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C604" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D604" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E604" s="11">
         <v>8.2352900000000007E-2</v>
@@ -17520,7 +17539,7 @@
         <v>1</v>
       </c>
       <c r="D605" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E605" s="11">
         <v>9.0196100000000001E-2</v>
@@ -17540,7 +17559,7 @@
         <v>36</v>
       </c>
       <c r="B606" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C606" s="8" t="s">
         <v>1</v>
@@ -17592,7 +17611,7 @@
         <v>36</v>
       </c>
       <c r="B608" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C608" s="8" t="s">
         <v>1</v>
@@ -17826,13 +17845,13 @@
         <v>36</v>
       </c>
       <c r="B617" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C617" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D617" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E617" s="11">
         <v>0.145098</v>
@@ -17858,7 +17877,7 @@
         <v>1</v>
       </c>
       <c r="D618" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E618" s="11">
         <v>0.22745099999999999</v>
@@ -17878,13 +17897,13 @@
         <v>36</v>
       </c>
       <c r="B619" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C619" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D619" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E619" s="11">
         <v>0.12941179999999999</v>
@@ -17930,13 +17949,13 @@
         <v>36</v>
       </c>
       <c r="B621" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C621" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D621" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E621" s="11">
         <v>0.14117650000000001</v>
@@ -18066,7 +18085,7 @@
         <v>1</v>
       </c>
       <c r="D626" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E626" s="11">
         <v>8.6274500000000004E-2</v>
@@ -18086,7 +18105,7 @@
         <v>36</v>
       </c>
       <c r="B627" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C627" s="8" t="s">
         <v>1</v>
@@ -18268,13 +18287,13 @@
         <v>37</v>
       </c>
       <c r="B634" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C634" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D634" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E634" s="11">
         <v>0.17786560000000001</v>
@@ -18300,7 +18319,7 @@
         <v>13</v>
       </c>
       <c r="D635" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E635" s="11">
         <v>0.21739130000000001</v>
@@ -18320,7 +18339,7 @@
         <v>37</v>
       </c>
       <c r="B636" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C636" s="8" t="s">
         <v>13</v>
@@ -18372,7 +18391,7 @@
         <v>37</v>
       </c>
       <c r="B638" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C638" s="8" t="s">
         <v>13</v>
@@ -18606,13 +18625,13 @@
         <v>37</v>
       </c>
       <c r="B647" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C647" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D647" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E647" s="11">
         <v>0.22924900000000001</v>
@@ -18638,7 +18657,7 @@
         <v>13</v>
       </c>
       <c r="D648" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E648" s="11">
         <v>0.3438735</v>
@@ -18658,13 +18677,13 @@
         <v>37</v>
       </c>
       <c r="B649" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C649" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D649" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E649" s="11">
         <v>0.22529640000000001</v>
@@ -18710,13 +18729,13 @@
         <v>37</v>
       </c>
       <c r="B651" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C651" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D651" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E651" s="11">
         <v>0.22529640000000001</v>
@@ -18846,7 +18865,7 @@
         <v>13</v>
       </c>
       <c r="D656" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E656" s="11">
         <v>0.13438739999999999</v>
@@ -18866,7 +18885,7 @@
         <v>37</v>
       </c>
       <c r="B657" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C657" s="8" t="s">
         <v>13</v>
@@ -19048,13 +19067,13 @@
         <v>38</v>
       </c>
       <c r="B664" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C664" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D664" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E664" s="11">
         <v>0.16535430000000001</v>
@@ -19080,7 +19099,7 @@
         <v>9</v>
       </c>
       <c r="D665" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E665" s="11">
         <v>0.1456693</v>
@@ -19100,7 +19119,7 @@
         <v>38</v>
       </c>
       <c r="B666" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C666" s="8" t="s">
         <v>9</v>
@@ -19152,7 +19171,7 @@
         <v>38</v>
       </c>
       <c r="B668" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C668" s="8" t="s">
         <v>9</v>
@@ -19386,13 +19405,13 @@
         <v>38</v>
       </c>
       <c r="B677" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C677" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D677" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E677" s="11">
         <v>0.1771654</v>
@@ -19418,7 +19437,7 @@
         <v>9</v>
       </c>
       <c r="D678" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E678" s="11">
         <v>0.21653539999999999</v>
@@ -19438,13 +19457,13 @@
         <v>38</v>
       </c>
       <c r="B679" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C679" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D679" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E679" s="11">
         <v>0.2362205</v>
@@ -19490,13 +19509,13 @@
         <v>38</v>
       </c>
       <c r="B681" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C681" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D681" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E681" s="11">
         <v>0.2086614</v>
@@ -19626,7 +19645,7 @@
         <v>9</v>
       </c>
       <c r="D686" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E686" s="11">
         <v>0.1181102</v>
@@ -19646,7 +19665,7 @@
         <v>38</v>
       </c>
       <c r="B687" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C687" s="8" t="s">
         <v>9</v>
@@ -19828,13 +19847,13 @@
         <v>26</v>
       </c>
       <c r="B694" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C694" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D694" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E694" s="11">
         <v>8.3003999999999994E-2</v>
@@ -19860,7 +19879,7 @@
         <v>8</v>
       </c>
       <c r="D695" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E695" s="11">
         <v>8.3003999999999994E-2</v>
@@ -19880,7 +19899,7 @@
         <v>26</v>
       </c>
       <c r="B696" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C696" s="8" t="s">
         <v>8</v>
@@ -19932,7 +19951,7 @@
         <v>26</v>
       </c>
       <c r="B698" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C698" s="8" t="s">
         <v>8</v>
@@ -20166,13 +20185,13 @@
         <v>26</v>
       </c>
       <c r="B707" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C707" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D707" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E707" s="11">
         <v>9.0909100000000007E-2</v>
@@ -20198,7 +20217,7 @@
         <v>8</v>
       </c>
       <c r="D708" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E708" s="11">
         <v>0.1106719</v>
@@ -20218,13 +20237,13 @@
         <v>26</v>
       </c>
       <c r="B709" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C709" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D709" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E709" s="11">
         <v>0.10276680000000001</v>
@@ -20270,13 +20289,13 @@
         <v>26</v>
       </c>
       <c r="B711" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C711" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D711" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E711" s="11">
         <v>0.1146245</v>
@@ -20406,7 +20425,7 @@
         <v>8</v>
       </c>
       <c r="D716" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E716" s="11">
         <v>7.9051399999999994E-2</v>
@@ -20426,7 +20445,7 @@
         <v>26</v>
       </c>
       <c r="B717" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C717" s="8" t="s">
         <v>8</v>
@@ -20559,7 +20578,7 @@
         <v>27</v>
       </c>
       <c r="C722" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D722" s="8" t="s">
         <v>2</v>
@@ -20585,7 +20604,7 @@
         <v>28</v>
       </c>
       <c r="C723" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D723" s="8" t="s">
         <v>0</v>
@@ -20608,13 +20627,13 @@
         <v>45</v>
       </c>
       <c r="B724" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C724" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D724" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E724" s="11">
         <v>0.1254902</v>
@@ -20637,10 +20656,10 @@
         <v>43</v>
       </c>
       <c r="C725" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D725" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E725" s="11">
         <v>0.14117650000000001</v>
@@ -20660,10 +20679,10 @@
         <v>45</v>
       </c>
       <c r="B726" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C726" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D726" s="8" t="s">
         <v>20</v>
@@ -20689,7 +20708,7 @@
         <v>29</v>
       </c>
       <c r="C727" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D727" s="8" t="s">
         <v>7</v>
@@ -20712,10 +20731,10 @@
         <v>45</v>
       </c>
       <c r="B728" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C728" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D728" s="8" t="s">
         <v>22</v>
@@ -20741,7 +20760,7 @@
         <v>30</v>
       </c>
       <c r="C729" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D729" s="8" t="s">
         <v>6</v>
@@ -20767,7 +20786,7 @@
         <v>25</v>
       </c>
       <c r="C730" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D730" s="8" t="s">
         <v>5</v>
@@ -20793,7 +20812,7 @@
         <v>31</v>
       </c>
       <c r="C731" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D731" s="8" t="s">
         <v>16</v>
@@ -20819,7 +20838,7 @@
         <v>23</v>
       </c>
       <c r="C732" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D732" s="8" t="s">
         <v>3</v>
@@ -20845,7 +20864,7 @@
         <v>32</v>
       </c>
       <c r="C733" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D733" s="8" t="s">
         <v>17</v>
@@ -20871,7 +20890,7 @@
         <v>33</v>
       </c>
       <c r="C734" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D734" s="8" t="s">
         <v>18</v>
@@ -20897,7 +20916,7 @@
         <v>34</v>
       </c>
       <c r="C735" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D735" s="8" t="s">
         <v>21</v>
@@ -20923,7 +20942,7 @@
         <v>24</v>
       </c>
       <c r="C736" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D736" s="8" t="s">
         <v>14</v>
@@ -20946,13 +20965,13 @@
         <v>45</v>
       </c>
       <c r="B737" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C737" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D737" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E737" s="11">
         <v>0.1803922</v>
@@ -20975,10 +20994,10 @@
         <v>44</v>
       </c>
       <c r="C738" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D738" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E738" s="11">
         <v>0.18823529999999999</v>
@@ -20998,13 +21017,13 @@
         <v>45</v>
       </c>
       <c r="B739" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C739" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D739" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E739" s="11">
         <v>0.19607840000000001</v>
@@ -21027,7 +21046,7 @@
         <v>35</v>
       </c>
       <c r="C740" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D740" s="8" t="s">
         <v>12</v>
@@ -21050,13 +21069,13 @@
         <v>45</v>
       </c>
       <c r="B741" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C741" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D741" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E741" s="11">
         <v>0.19607840000000001</v>
@@ -21079,7 +21098,7 @@
         <v>36</v>
       </c>
       <c r="C742" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D742" s="8" t="s">
         <v>1</v>
@@ -21105,7 +21124,7 @@
         <v>37</v>
       </c>
       <c r="C743" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D743" s="8" t="s">
         <v>13</v>
@@ -21131,7 +21150,7 @@
         <v>38</v>
       </c>
       <c r="C744" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D744" s="8" t="s">
         <v>9</v>
@@ -21157,7 +21176,7 @@
         <v>26</v>
       </c>
       <c r="C745" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D745" s="8" t="s">
         <v>8</v>
@@ -21183,10 +21202,10 @@
         <v>45</v>
       </c>
       <c r="C746" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D746" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E746" s="11">
         <v>0.34117649999999999</v>
@@ -21206,10 +21225,10 @@
         <v>45</v>
       </c>
       <c r="B747" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C747" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D747" s="8" t="s">
         <v>19</v>
@@ -21235,7 +21254,7 @@
         <v>39</v>
       </c>
       <c r="C748" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D748" s="8" t="s">
         <v>15</v>
@@ -21261,7 +21280,7 @@
         <v>40</v>
       </c>
       <c r="C749" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D749" s="8" t="s">
         <v>10</v>
@@ -21287,7 +21306,7 @@
         <v>41</v>
       </c>
       <c r="C750" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D750" s="8" t="s">
         <v>11</v>
@@ -21313,7 +21332,7 @@
         <v>42</v>
       </c>
       <c r="C751" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D751" s="8" t="s">
         <v>4</v>
@@ -21333,7 +21352,7 @@
     </row>
     <row r="752" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A752" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B752" s="8" t="s">
         <v>27</v>
@@ -21359,7 +21378,7 @@
     </row>
     <row r="753" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A753" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B753" s="8" t="s">
         <v>28</v>
@@ -21385,16 +21404,16 @@
     </row>
     <row r="754" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A754" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B754" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C754" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D754" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E754" s="11">
         <v>0.16269839999999999</v>
@@ -21411,7 +21430,7 @@
     </row>
     <row r="755" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A755" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B755" s="8" t="s">
         <v>43</v>
@@ -21420,7 +21439,7 @@
         <v>19</v>
       </c>
       <c r="D755" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E755" s="11">
         <v>0.17460319999999999</v>
@@ -21437,10 +21456,10 @@
     </row>
     <row r="756" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A756" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B756" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C756" s="8" t="s">
         <v>19</v>
@@ -21463,7 +21482,7 @@
     </row>
     <row r="757" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A757" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B757" s="8" t="s">
         <v>29</v>
@@ -21489,10 +21508,10 @@
     </row>
     <row r="758" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A758" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B758" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C758" s="8" t="s">
         <v>19</v>
@@ -21515,7 +21534,7 @@
     </row>
     <row r="759" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A759" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B759" s="8" t="s">
         <v>30</v>
@@ -21541,7 +21560,7 @@
     </row>
     <row r="760" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A760" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B760" s="8" t="s">
         <v>25</v>
@@ -21567,7 +21586,7 @@
     </row>
     <row r="761" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A761" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B761" s="8" t="s">
         <v>31</v>
@@ -21593,7 +21612,7 @@
     </row>
     <row r="762" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A762" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B762" s="8" t="s">
         <v>23</v>
@@ -21619,7 +21638,7 @@
     </row>
     <row r="763" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A763" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B763" s="8" t="s">
         <v>32</v>
@@ -21645,7 +21664,7 @@
     </row>
     <row r="764" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A764" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B764" s="8" t="s">
         <v>33</v>
@@ -21671,7 +21690,7 @@
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A765" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B765" s="8" t="s">
         <v>34</v>
@@ -21697,7 +21716,7 @@
     </row>
     <row r="766" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A766" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B766" s="8" t="s">
         <v>24</v>
@@ -21723,16 +21742,16 @@
     </row>
     <row r="767" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A767" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B767" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C767" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D767" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E767" s="11">
         <v>0.24206349999999999</v>
@@ -21749,7 +21768,7 @@
     </row>
     <row r="768" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A768" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B768" s="8" t="s">
         <v>44</v>
@@ -21758,7 +21777,7 @@
         <v>19</v>
       </c>
       <c r="D768" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E768" s="11">
         <v>0.26587300000000003</v>
@@ -21775,16 +21794,16 @@
     </row>
     <row r="769" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A769" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B769" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C769" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D769" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E769" s="11">
         <v>0.2142857</v>
@@ -21801,7 +21820,7 @@
     </row>
     <row r="770" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A770" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B770" s="8" t="s">
         <v>35</v>
@@ -21827,16 +21846,16 @@
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A771" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B771" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C771" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D771" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E771" s="11">
         <v>0.234127</v>
@@ -21853,7 +21872,7 @@
     </row>
     <row r="772" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A772" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B772" s="8" t="s">
         <v>36</v>
@@ -21879,7 +21898,7 @@
     </row>
     <row r="773" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A773" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B773" s="8" t="s">
         <v>37</v>
@@ -21905,7 +21924,7 @@
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A774" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B774" s="8" t="s">
         <v>38</v>
@@ -21931,7 +21950,7 @@
     </row>
     <row r="775" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A775" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B775" s="8" t="s">
         <v>26</v>
@@ -21957,7 +21976,7 @@
     </row>
     <row r="776" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A776" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B776" s="8" t="s">
         <v>45</v>
@@ -21966,7 +21985,7 @@
         <v>19</v>
       </c>
       <c r="D776" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E776" s="11">
         <v>0.17857139999999999</v>
@@ -21983,10 +22002,10 @@
     </row>
     <row r="777" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A777" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B777" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C777" s="8" t="s">
         <v>19</v>
@@ -22009,7 +22028,7 @@
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A778" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B778" s="8" t="s">
         <v>39</v>
@@ -22035,7 +22054,7 @@
     </row>
     <row r="779" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A779" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B779" s="8" t="s">
         <v>40</v>
@@ -22061,7 +22080,7 @@
     </row>
     <row r="780" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A780" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B780" s="8" t="s">
         <v>41</v>
@@ -22087,7 +22106,7 @@
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A781" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B781" s="8" t="s">
         <v>42</v>
@@ -22168,13 +22187,13 @@
         <v>39</v>
       </c>
       <c r="B784" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C784" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D784" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E784" s="11">
         <v>5.4901999999999999E-2</v>
@@ -22200,7 +22219,7 @@
         <v>15</v>
       </c>
       <c r="D785" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E785" s="11">
         <v>7.0588200000000004E-2</v>
@@ -22220,7 +22239,7 @@
         <v>39</v>
       </c>
       <c r="B786" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C786" s="8" t="s">
         <v>15</v>
@@ -22272,7 +22291,7 @@
         <v>39</v>
       </c>
       <c r="B788" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C788" s="8" t="s">
         <v>15</v>
@@ -22506,13 +22525,13 @@
         <v>39</v>
       </c>
       <c r="B797" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C797" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D797" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E797" s="11">
         <v>9.8039200000000007E-2</v>
@@ -22538,7 +22557,7 @@
         <v>15</v>
       </c>
       <c r="D798" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E798" s="11">
         <v>0.1568628</v>
@@ -22558,13 +22577,13 @@
         <v>39</v>
       </c>
       <c r="B799" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C799" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D799" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E799" s="11">
         <v>9.4117599999999996E-2</v>
@@ -22610,13 +22629,13 @@
         <v>39</v>
       </c>
       <c r="B801" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C801" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D801" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E801" s="11">
         <v>7.8431399999999998E-2</v>
@@ -22746,7 +22765,7 @@
         <v>15</v>
       </c>
       <c r="D806" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E806" s="11">
         <v>6.6666699999999995E-2</v>
@@ -22766,7 +22785,7 @@
         <v>39</v>
       </c>
       <c r="B807" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C807" s="8" t="s">
         <v>15</v>
@@ -22948,13 +22967,13 @@
         <v>40</v>
       </c>
       <c r="B814" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C814" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D814" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E814" s="11">
         <v>7.5098799999999993E-2</v>
@@ -22980,7 +22999,7 @@
         <v>10</v>
       </c>
       <c r="D815" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E815" s="11">
         <v>0.10276680000000001</v>
@@ -23000,7 +23019,7 @@
         <v>40</v>
       </c>
       <c r="B816" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C816" s="8" t="s">
         <v>10</v>
@@ -23052,7 +23071,7 @@
         <v>40</v>
       </c>
       <c r="B818" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C818" s="8" t="s">
         <v>10</v>
@@ -23286,13 +23305,13 @@
         <v>40</v>
       </c>
       <c r="B827" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C827" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D827" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E827" s="11">
         <v>0.13043479999999999</v>
@@ -23318,7 +23337,7 @@
         <v>10</v>
       </c>
       <c r="D828" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E828" s="11">
         <v>0.16205530000000001</v>
@@ -23338,13 +23357,13 @@
         <v>40</v>
       </c>
       <c r="B829" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C829" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D829" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E829" s="11">
         <v>0.1185771</v>
@@ -23390,13 +23409,13 @@
         <v>40</v>
       </c>
       <c r="B831" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C831" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D831" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E831" s="11">
         <v>0.13043479999999999</v>
@@ -23526,7 +23545,7 @@
         <v>10</v>
       </c>
       <c r="D836" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E836" s="11">
         <v>9.0909100000000007E-2</v>
@@ -23546,7 +23565,7 @@
         <v>40</v>
       </c>
       <c r="B837" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C837" s="8" t="s">
         <v>10</v>
@@ -23728,13 +23747,13 @@
         <v>41</v>
       </c>
       <c r="B844" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C844" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D844" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E844" s="11">
         <v>0.1529412</v>
@@ -23760,7 +23779,7 @@
         <v>11</v>
       </c>
       <c r="D845" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E845" s="11">
         <v>0.2078431</v>
@@ -23780,7 +23799,7 @@
         <v>41</v>
       </c>
       <c r="B846" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C846" s="8" t="s">
         <v>11</v>
@@ -23832,7 +23851,7 @@
         <v>41</v>
       </c>
       <c r="B848" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C848" s="8" t="s">
         <v>11</v>
@@ -24066,13 +24085,13 @@
         <v>41</v>
       </c>
       <c r="B857" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C857" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D857" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E857" s="11">
         <v>0.22745099999999999</v>
@@ -24098,7 +24117,7 @@
         <v>11</v>
       </c>
       <c r="D858" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E858" s="11">
         <v>0.29411769999999998</v>
@@ -24118,13 +24137,13 @@
         <v>41</v>
       </c>
       <c r="B859" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C859" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D859" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E859" s="11">
         <v>0.18823529999999999</v>
@@ -24170,13 +24189,13 @@
         <v>41</v>
       </c>
       <c r="B861" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C861" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D861" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E861" s="11">
         <v>0.22745099999999999</v>
@@ -24306,7 +24325,7 @@
         <v>11</v>
       </c>
       <c r="D866" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E866" s="11">
         <v>0.14117650000000001</v>
@@ -24326,7 +24345,7 @@
         <v>41</v>
       </c>
       <c r="B867" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C867" s="8" t="s">
         <v>11</v>
@@ -24508,13 +24527,13 @@
         <v>42</v>
       </c>
       <c r="B874" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C874" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D874" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E874" s="11">
         <v>0.1106719</v>
@@ -24540,7 +24559,7 @@
         <v>4</v>
       </c>
       <c r="D875" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E875" s="11">
         <v>0.16996049999999999</v>
@@ -24560,7 +24579,7 @@
         <v>42</v>
       </c>
       <c r="B876" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C876" s="8" t="s">
         <v>4</v>
@@ -24612,7 +24631,7 @@
         <v>42</v>
       </c>
       <c r="B878" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C878" s="8" t="s">
         <v>4</v>
@@ -24846,13 +24865,13 @@
         <v>42</v>
       </c>
       <c r="B887" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C887" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D887" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E887" s="11">
         <v>0.14229249999999999</v>
@@ -24878,7 +24897,7 @@
         <v>4</v>
       </c>
       <c r="D888" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E888" s="11">
         <v>0.16996049999999999</v>
@@ -24898,13 +24917,13 @@
         <v>42</v>
       </c>
       <c r="B889" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C889" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D889" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E889" s="11">
         <v>0.14229249999999999</v>
@@ -24950,13 +24969,13 @@
         <v>42</v>
       </c>
       <c r="B891" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C891" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D891" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E891" s="11">
         <v>0.17391300000000001</v>
@@ -25086,7 +25105,7 @@
         <v>4</v>
       </c>
       <c r="D896" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E896" s="11">
         <v>0.1225296</v>
@@ -25106,7 +25125,7 @@
         <v>42</v>
       </c>
       <c r="B897" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C897" s="8" t="s">
         <v>4</v>
